--- a/output/261001-전남대-손현철/261001-세트1-비교견적서1.xlsx
+++ b/output/261001-전남대-손현철/261001-세트1-비교견적서1.xlsx
@@ -4504,7 +4504,7 @@
       </c>
       <c r="H20" s="8">
         <f>SUM(H18:H19)</f>
-        <v>2.35822e+06</v>
+        <v>2358224</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
